--- a/exo_records.xlsx
+++ b/exo_records.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Records" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Records" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S104"/>
+  <dimension ref="A1:S111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8105,6 +8105,517 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:03:57</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>882.9</v>
+      </c>
+      <c r="P105" s="3" t="n">
+        <v>882.9</v>
+      </c>
+      <c r="Q105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S105" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:04:01</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>899.7</v>
+      </c>
+      <c r="P106" s="3" t="n">
+        <v>897.8</v>
+      </c>
+      <c r="Q106" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R106" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="S106" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:04:04</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>1320.7</v>
+      </c>
+      <c r="P107" s="3" t="n">
+        <v>1272.9</v>
+      </c>
+      <c r="Q107" s="3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="R107" s="3" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="S107" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:04:07</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="M108" s="3" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>67.18000000000001</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>2355.4</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>2189.9</v>
+      </c>
+      <c r="Q108" s="3" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="R108" s="3" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="S108" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:04:10</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="M109" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N109" s="3" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>994.4</v>
+      </c>
+      <c r="P109" s="3" t="n">
+        <v>982.3</v>
+      </c>
+      <c r="Q109" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R109" s="3" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="S109" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:04:13</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L110" s="3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="M110" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N110" s="3" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>975.7</v>
+      </c>
+      <c r="P110" s="3" t="n">
+        <v>965.6</v>
+      </c>
+      <c r="Q110" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R110" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="S110" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>未命名</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>擺位</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>bare</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15 01:04:16</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="M111" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N111" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>970.1</v>
+      </c>
+      <c r="P111" s="3" t="n">
+        <v>960.7</v>
+      </c>
+      <c r="Q111" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R111" s="3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="S111" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
